--- a/data/trans_dic/P02E$nadie-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P02E$nadie-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que no tienen ayuda al cuidado por parte de una persona externa</t>
+          <t>Hogares que no tienen ayuda al cuidado por parte de una persona externa (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>93,64; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>78,71; 97,49</t>
+          <t>77,38; 97,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76,45; 97,38</t>
+          <t>77,29; 97,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84,08; 98,29</t>
+          <t>83,62; 98,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>88,23; 98,02</t>
+          <t>87,53; 98,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,31; 90,18</t>
+          <t>74,62; 90,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,63; 98,88</t>
+          <t>89,87; 98,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>87,81; 96,59</t>
+          <t>88,01; 96,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>78,9; 90,79</t>
+          <t>79,42; 91,07</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>77,18; 89,25</t>
+          <t>76,74; 88,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>87,37; 94,72</t>
+          <t>87,64; 94,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88,46; 96,5</t>
+          <t>88,69; 96,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86,1; 92,87</t>
+          <t>86,23; 93,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>87,16; 93,38</t>
+          <t>87,5; 93,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>87,23; 94,08</t>
+          <t>87,62; 94,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,07; 90,47</t>
+          <t>84,79; 90,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>88,59; 93,23</t>
+          <t>88,44; 93,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>89,5; 94,31</t>
+          <t>89,33; 94,44</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>87,97; 95,01</t>
+          <t>88,45; 94,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>89,23; 95,02</t>
+          <t>89,58; 94,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88,98; 95,2</t>
+          <t>88,52; 94,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>90,61; 95,56</t>
+          <t>90,66; 95,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>92,28; 96,25</t>
+          <t>92,53; 96,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>84,61; 91,45</t>
+          <t>85,19; 91,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>90,87; 94,86</t>
+          <t>90,75; 94,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>91,98; 95,22</t>
+          <t>92,15; 95,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>87,54; 92,26</t>
+          <t>87,94; 92,19</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>90,68; 98,29</t>
+          <t>90,18; 98,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>90,79; 97,12</t>
+          <t>91,02; 96,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85,58; 95,13</t>
+          <t>85,91; 94,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87,86; 97,49</t>
+          <t>87,3; 97,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>90,88; 96,76</t>
+          <t>91,34; 97,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,57; 95,58</t>
+          <t>87,22; 95,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,16; 97,22</t>
+          <t>90,66; 97,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>92,51; 96,36</t>
+          <t>92,49; 96,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>88,19; 94,47</t>
+          <t>88,16; 94,3</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>69,8; 100,0</t>
+          <t>67,72; 100,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>75,64; 95,59</t>
+          <t>76,05; 95,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75,36; 97,19</t>
+          <t>75,52; 97,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83,24; 98,19</t>
+          <t>84,9; 98,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>76,95; 91,21</t>
+          <t>75,5; 90,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,28; 89,0</t>
+          <t>66,23; 88,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,86; 97,59</t>
+          <t>86,15; 97,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>78,04; 90,64</t>
+          <t>79,2; 90,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>74,23; 90,16</t>
+          <t>74,08; 89,75</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41,52; 87,91</t>
+          <t>41,22; 87,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>46,43; 86,38</t>
+          <t>46,12; 86,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>61,36; 95,37</t>
+          <t>62,07; 95,35</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>81,36; 98,09</t>
+          <t>81,66; 98,07</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>74,46; 93,83</t>
+          <t>73,16; 93,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>67,45; 94,28</t>
+          <t>65,96; 94,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>75,81; 92,71</t>
+          <t>76,28; 93,62</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>69,67; 88,02</t>
+          <t>69,4; 87,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>70,72; 91,17</t>
+          <t>70,57; 90,05</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>49,93; 90,76</t>
+          <t>50,89; 90,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>25,22; 84,73</t>
+          <t>25,43; 84,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40,09; 89,22</t>
+          <t>38,33; 90,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41,91; 82,12</t>
+          <t>42,54; 82,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>41,55; 74,09</t>
+          <t>40,85; 72,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,01; 76,92</t>
+          <t>43,53; 76,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,16; 81,19</t>
+          <t>49,81; 80,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>44,98; 70,9</t>
+          <t>43,68; 70,34</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>48,46; 75,61</t>
+          <t>49,26; 77,69</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>87,2; 92,21</t>
+          <t>86,69; 91,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>89,52; 93,02</t>
+          <t>89,42; 93,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>89,27; 93,29</t>
+          <t>89,32; 93,53</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>89,69; 93,36</t>
+          <t>89,92; 93,31</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>90,06; 93,08</t>
+          <t>90,16; 93,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>85,53; 89,65</t>
+          <t>85,62; 89,6</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>89,37; 92,3</t>
+          <t>89,42; 92,39</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>90,37; 92,68</t>
+          <t>90,47; 92,72</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>87,71; 90,44</t>
+          <t>87,64; 90,46</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que no tienen ayuda al cuidado por parte de una persona externa</t>
+          <t>Hogares que no tienen ayuda al cuidado por parte de una persona externa (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>28137; 30046</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>32275; 39975</t>
+          <t>31727; 39984</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31157; 39687</t>
+          <t>31502; 39689</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42508; 49691</t>
+          <t>42275; 49657</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>89666; 99617</t>
+          <t>88961; 99625</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>67678; 81045</t>
+          <t>67058; 81126</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>71440; 79700</t>
+          <t>72440; 79699</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>125251; 137767</t>
+          <t>125539; 137683</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>103067; 118588</t>
+          <t>103738; 118962</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>128767; 148916</t>
+          <t>128036; 148429</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>187190; 202938</t>
+          <t>187751; 202972</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>153307; 167236</t>
+          <t>153710; 167539</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>260793; 281314</t>
+          <t>261185; 281784</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>340386; 364681</t>
+          <t>341732; 365788</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>255948; 276038</t>
+          <t>257071; 275887</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>394920; 424970</t>
+          <t>398313; 425408</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>535779; 563845</t>
+          <t>534847; 562685</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>417722; 440170</t>
+          <t>416899; 440757</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>238030; 257073</t>
+          <t>239304; 256810</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>369842; 393824</t>
+          <t>371275; 393524</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>277428; 296816</t>
+          <t>276003; 295651</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>355322; 374729</t>
+          <t>355495; 376063</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>529722; 552536</t>
+          <t>531185; 553347</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>344633; 372516</t>
+          <t>347004; 373128</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>602218; 628615</t>
+          <t>601392; 628281</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>909202; 941282</t>
+          <t>910903; 940743</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>629544; 663455</t>
+          <t>632398; 662956</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>100127; 108526</t>
+          <t>99568; 108604</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>207627; 222109</t>
+          <t>208170; 221641</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>134256; 149246</t>
+          <t>134781; 148617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>106170; 117812</t>
+          <t>105499; 117277</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>237782; 253167</t>
+          <t>238976; 254030</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>159601; 174194</t>
+          <t>158970; 173839</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>210822; 224822</t>
+          <t>209665; 225019</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>453620; 472503</t>
+          <t>453529; 472399</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>299072; 320366</t>
+          <t>298977; 319816</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12530; 17951</t>
+          <t>12157; 17951</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>37174; 46979</t>
+          <t>37375; 46948</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30326; 39111</t>
+          <t>30392; 39136</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>55774; 65791</t>
+          <t>56890; 65956</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>77358; 91694</t>
+          <t>75899; 91372</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37634; 50535</t>
+          <t>37607; 50068</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>72943; 82914</t>
+          <t>73194; 83116</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>116802; 135663</t>
+          <t>118542; 135802</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>72022; 87476</t>
+          <t>71877; 87072</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5884; 12460</t>
+          <t>5842; 12379</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10350; 19257</t>
+          <t>10281; 19221</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13036; 20262</t>
+          <t>13188; 20257</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>38185; 46032</t>
+          <t>38324; 46024</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>35205; 44365</t>
+          <t>34592; 44341</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24588; 34367</t>
+          <t>24043; 34396</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>46323; 56652</t>
+          <t>46613; 57205</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>48475; 61241</t>
+          <t>48289; 60801</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>40802; 52605</t>
+          <t>40718; 51956</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>8087; 14701</t>
+          <t>8244; 14636</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3771; 12666</t>
+          <t>3802; 12687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4992; 11110</t>
+          <t>4774; 11278</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10657; 20884</t>
+          <t>10819; 20957</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>17131; 30549</t>
+          <t>16841; 30004</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19311; 34537</t>
+          <t>19546; 34149</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20880; 33798</t>
+          <t>20735; 33421</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>25268; 39833</t>
+          <t>24537; 39516</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>27793; 43365</t>
+          <t>28252; 44555</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>546033; 577409</t>
+          <t>542866; 575356</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>881615; 916099</t>
+          <t>880605; 917356</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>675488; 705880</t>
+          <t>675867; 707739</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>902148; 938991</t>
+          <t>904399; 938538</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1366090; 1411974</t>
+          <t>1367614; 1410901</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>950221; 995994</t>
+          <t>951264; 995468</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1458464; 1506307</t>
+          <t>1459284; 1507798</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2260750; 2318630</t>
+          <t>2263198; 2319630</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1638097; 1689040</t>
+          <t>1636825; 1689541</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P02E$nadie-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P02E$nadie-Edad-trans_dic.xlsx
@@ -683,42 +683,42 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>77,38; 97,51</t>
+          <t>78,87; 97,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77,29; 97,38</t>
+          <t>76,8; 97,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>83,62; 98,22</t>
+          <t>83,18; 98,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>87,53; 98,02</t>
+          <t>88,08; 98,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,62; 90,27</t>
+          <t>75,2; 90,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,87; 98,88</t>
+          <t>88,82; 98,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>88,01; 96,53</t>
+          <t>87,87; 96,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>79,42; 91,07</t>
+          <t>78,69; 90,51</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>76,74; 88,96</t>
+          <t>77,16; 88,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>87,64; 94,74</t>
+          <t>87,25; 94,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88,69; 96,67</t>
+          <t>89,37; 96,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86,23; 93,03</t>
+          <t>86,37; 93,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>87,5; 93,66</t>
+          <t>87,29; 93,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>87,62; 94,03</t>
+          <t>87,41; 94,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,79; 90,56</t>
+          <t>84,66; 90,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>88,44; 93,04</t>
+          <t>88,58; 93,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>89,33; 94,44</t>
+          <t>89,44; 94,27</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>88,45; 94,92</t>
+          <t>88,61; 95,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>89,58; 94,95</t>
+          <t>89,59; 94,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88,52; 94,83</t>
+          <t>89,21; 95,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>90,66; 95,9</t>
+          <t>90,5; 95,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>92,53; 96,39</t>
+          <t>92,42; 96,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>85,19; 91,6</t>
+          <t>85,45; 91,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>90,75; 94,81</t>
+          <t>90,91; 94,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>92,15; 95,17</t>
+          <t>91,86; 95,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>87,94; 92,19</t>
+          <t>87,95; 92,17</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>90,18; 98,36</t>
+          <t>90,21; 98,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>91,02; 96,91</t>
+          <t>90,81; 96,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85,91; 94,73</t>
+          <t>86,22; 95,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87,3; 97,05</t>
+          <t>87,75; 97,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>91,34; 97,09</t>
+          <t>91,43; 97,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,22; 95,38</t>
+          <t>87,06; 95,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,66; 97,3</t>
+          <t>91,33; 97,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>92,49; 96,34</t>
+          <t>92,33; 96,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>88,16; 94,3</t>
+          <t>88,24; 94,43</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>67,72; 100,0</t>
+          <t>67,85; 100,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>76,05; 95,53</t>
+          <t>73,33; 94,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75,52; 97,25</t>
+          <t>75,76; 97,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84,9; 98,43</t>
+          <t>84,58; 98,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>75,5; 90,89</t>
+          <t>75,63; 90,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,23; 88,18</t>
+          <t>65,2; 88,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,15; 97,83</t>
+          <t>85,61; 97,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>79,2; 90,73</t>
+          <t>79,14; 91,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>74,08; 89,75</t>
+          <t>74,49; 90,31</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41,22; 87,34</t>
+          <t>40,3; 87,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>46,12; 86,22</t>
+          <t>43,07; 85,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>62,07; 95,35</t>
+          <t>60,97; 95,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>81,66; 98,07</t>
+          <t>79,82; 97,77</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>73,16; 93,78</t>
+          <t>73,17; 93,72</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>65,96; 94,36</t>
+          <t>65,12; 92,15</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>76,28; 93,62</t>
+          <t>75,39; 93,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>69,4; 87,39</t>
+          <t>69,08; 88,38</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>70,57; 90,05</t>
+          <t>69,99; 91,0</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>50,89; 90,35</t>
+          <t>49,51; 89,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>25,43; 84,87</t>
+          <t>28,71; 84,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38,33; 90,56</t>
+          <t>40,02; 93,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42,54; 82,41</t>
+          <t>43,97; 82,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>40,85; 72,77</t>
+          <t>43,42; 72,17</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,53; 76,06</t>
+          <t>44,08; 78,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,81; 80,29</t>
+          <t>50,81; 80,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>43,68; 70,34</t>
+          <t>44,01; 72,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>49,26; 77,69</t>
+          <t>48,49; 76,44</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>86,69; 91,88</t>
+          <t>87,12; 92,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>89,42; 93,15</t>
+          <t>89,47; 93,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>89,32; 93,53</t>
+          <t>89,18; 93,27</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>89,92; 93,31</t>
+          <t>89,79; 93,35</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>90,16; 93,01</t>
+          <t>90,09; 92,92</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>85,62; 89,6</t>
+          <t>85,51; 89,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>89,42; 92,39</t>
+          <t>89,36; 92,31</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>90,47; 92,72</t>
+          <t>90,32; 92,62</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>87,64; 90,46</t>
+          <t>87,63; 90,59</t>
         </is>
       </c>
     </row>
@@ -1755,42 +1755,42 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31727; 39984</t>
+          <t>32341; 40019</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31502; 39689</t>
+          <t>31301; 39669</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42275; 49657</t>
+          <t>42053; 49670</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>88961; 99625</t>
+          <t>89520; 99625</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>67058; 81126</t>
+          <t>67584; 81023</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>72440; 79699</t>
+          <t>71593; 79630</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>125539; 137683</t>
+          <t>125328; 137701</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>103738; 118962</t>
+          <t>102786; 118226</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>128036; 148429</t>
+          <t>128736; 148250</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>187751; 202972</t>
+          <t>186921; 202738</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>153710; 167539</t>
+          <t>154876; 167557</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>261185; 281784</t>
+          <t>261631; 282416</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>341732; 365788</t>
+          <t>340910; 365056</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>257071; 275887</t>
+          <t>256469; 276280</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>398313; 425408</t>
+          <t>397683; 425353</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>534847; 562685</t>
+          <t>535735; 564655</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>416899; 440757</t>
+          <t>417420; 439967</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>239304; 256810</t>
+          <t>239739; 257071</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>371275; 393524</t>
+          <t>371308; 393487</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>276003; 295651</t>
+          <t>278136; 296212</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>355495; 376063</t>
+          <t>354876; 374589</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>531185; 553347</t>
+          <t>530531; 553336</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>347004; 373128</t>
+          <t>348054; 373776</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>601392; 628281</t>
+          <t>602451; 628601</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>910903; 940743</t>
+          <t>908071; 940077</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>632398; 662956</t>
+          <t>632481; 662797</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>99568; 108604</t>
+          <t>99602; 108504</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>208170; 221641</t>
+          <t>207685; 221698</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>134781; 148617</t>
+          <t>135265; 149572</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>105499; 117277</t>
+          <t>106044; 117740</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>238976; 254030</t>
+          <t>239220; 254155</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>158970; 173839</t>
+          <t>158672; 174713</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>209665; 225019</t>
+          <t>211213; 224356</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>453529; 472399</t>
+          <t>452708; 472671</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>298977; 319816</t>
+          <t>299268; 320258</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12157; 17951</t>
+          <t>12180; 17951</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>37375; 46948</t>
+          <t>36039; 46242</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30392; 39136</t>
+          <t>30486; 39184</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>56890; 65956</t>
+          <t>56675; 65951</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>75899; 91372</t>
+          <t>76028; 91228</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37607; 50068</t>
+          <t>37019; 50391</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>73194; 83116</t>
+          <t>72733; 82878</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>118542; 135802</t>
+          <t>118452; 136586</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>71877; 87072</t>
+          <t>72273; 87623</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5842; 12379</t>
+          <t>5711; 12345</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10281; 19221</t>
+          <t>9602; 19140</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13188; 20257</t>
+          <t>12953; 20276</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>38324; 46024</t>
+          <t>37462; 45885</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>34592; 44341</t>
+          <t>34597; 44313</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24043; 34396</t>
+          <t>23738; 33590</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>46613; 57205</t>
+          <t>46066; 57191</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>48289; 60801</t>
+          <t>48063; 61491</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>40718; 51956</t>
+          <t>40386; 52509</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>8244; 14636</t>
+          <t>8020; 14548</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3802; 12687</t>
+          <t>4292; 12645</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4774; 11278</t>
+          <t>4983; 11583</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10819; 20957</t>
+          <t>11181; 20925</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>16841; 30004</t>
+          <t>17902; 29758</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19546; 34149</t>
+          <t>19790; 35060</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20735; 33421</t>
+          <t>21152; 33693</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>24537; 39516</t>
+          <t>24724; 40829</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>28252; 44555</t>
+          <t>27809; 43842</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>542866; 575356</t>
+          <t>545566; 576200</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>880605; 917356</t>
+          <t>881128; 917470</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>675867; 707739</t>
+          <t>674813; 705713</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>904399; 938538</t>
+          <t>903129; 938878</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1367614; 1410901</t>
+          <t>1366515; 1409518</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>951264; 995468</t>
+          <t>950051; 994923</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1459284; 1507798</t>
+          <t>1458314; 1506480</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2263198; 2319630</t>
+          <t>2259547; 2316987</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1636825; 1689541</t>
+          <t>1636538; 1691819</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P02E$nadie-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P02E$nadie-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que no tienen ayuda al cuidado por parte de una persona externa (tasa de respuesta: 96,71%)</t>
+          <t>Población que no tiene ayuda al cuidado por parte de una persona externa (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1543,7 +1543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que no tienen ayuda al cuidado por parte de una persona externa (tasa de respuesta: 96,71%)</t>
+          <t>Población que no tiene ayuda al cuidado por parte de una persona externa (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
